--- a/data/trans_orig/P34B03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B03-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza una actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza una actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,52</t>
+          <t>1,16; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,99</t>
+          <t>1,55; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,24</t>
+          <t>1,47; 2,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,96</t>
+          <t>0,64; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,06</t>
+          <t>0,58; 1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,43</t>
+          <t>1,17; 1,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,63</t>
+          <t>1,16; 1,6</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,46</t>
+          <t>1,14; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,58</t>
+          <t>1,24; 1,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,71</t>
+          <t>1,15; 1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,61</t>
+          <t>0,38; 0,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,82</t>
+          <t>0,56; 0,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,74</t>
+          <t>0,35; 0,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,02</t>
+          <t>0,81; 1,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,14</t>
+          <t>0,95; 1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,12</t>
+          <t>0,72; 1,1</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,89</t>
+          <t>0,62; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,22</t>
+          <t>0,89; 1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,47</t>
+          <t>0,3; 0,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,77</t>
+          <t>0,54; 0,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,59</t>
+          <t>0,42; 0,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,89</t>
+          <t>0,7; 0,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,85</t>
+          <t>0,67; 0,86</t>
         </is>
       </c>
     </row>
@@ -1007,27 +1007,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,72</t>
+          <t>0,46; 0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,78</t>
+          <t>0,54; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,86</t>
+          <t>0,25; 0,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,34</t>
+          <t>0,17; 0,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,59</t>
+          <t>0,37; 0,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,65</t>
+          <t>0,49; 0,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,63</t>
+          <t>0,33; 0,63</t>
         </is>
       </c>
     </row>
@@ -1117,27 +1117,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,39</t>
+          <t>0,17; 0,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,52</t>
+          <t>0,3; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,5</t>
+          <t>0,31; 0,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,15; 0,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,36</t>
+          <t>0,18; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,33</t>
+          <t>0,19; 0,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,44</t>
+          <t>0,32; 0,45</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,42</t>
+          <t>0,11; 0,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,45</t>
+          <t>0,18; 0,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,44</t>
+          <t>0,26; 0,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,29</t>
+          <t>0,08; 0,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,41</t>
+          <t>0,18; 0,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,25</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,38</t>
+          <t>0,2; 0,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,39</t>
+          <t>0,06; 0,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,24</t>
+          <t>0,06; 0,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,31</t>
+          <t>0,12; 0,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,17 +1357,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,14</t>
+          <t>0,03; 0,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,18</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,21</t>
+          <t>0,06; 0,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,2</t>
+          <t>0,09; 0,19</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1447,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,82</t>
+          <t>0,69; 0,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 0,93</t>
+          <t>0,8; 0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,91</t>
+          <t>0,63; 0,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,35</t>
+          <t>0,28; 0,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,44</t>
+          <t>0,31; 0,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,71</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,65</t>
+          <t>0,51; 0,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B03-Edad-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,54</t>
+          <t>1,18; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,99</t>
+          <t>1,57; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,23</t>
+          <t>1,37; 2,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,66</t>
+          <t>0,41; 0,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,1</t>
+          <t>0,57; 1,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,08</t>
+          <t>0,84; 1,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,45</t>
+          <t>1,14; 1,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,6</t>
+          <t>1,05; 1,48</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,98</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,48</t>
+          <t>1,14; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,57</t>
+          <t>1,23; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,68</t>
+          <t>1,16; 1,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -812,22 +812,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,73</t>
+          <t>0,47; 0,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,01</t>
+          <t>0,82; 1,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,17</t>
+          <t>0,95; 1,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,1</t>
+          <t>0,84; 1,13</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -897,22 +897,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,88</t>
+          <t>0,63; 0,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,08</t>
+          <t>0,82; 1,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,2</t>
+          <t>0,86; 1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,48</t>
+          <t>0,3; 0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,6</t>
+          <t>0,4; 0,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,64</t>
+          <t>0,49; 0,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,89</t>
+          <t>0,71; 0,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,86</t>
+          <t>0,66; 0,83</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,14 +979,14 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>0,41</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,57</t>
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,73</t>
+          <t>0,47; 0,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,79</t>
+          <t>0,55; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,86</t>
+          <t>0,68; 0,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,33</t>
+          <t>0,17; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,6</t>
+          <t>0,37; 0,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,49</t>
+          <t>0,37; 0,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,49</t>
+          <t>0,34; 0,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,66</t>
+          <t>0,5; 0,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,63</t>
+          <t>0,54; 0,69</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1074,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>0,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,4</t>
+          <t>0,18; 0,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,54</t>
+          <t>0,28; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,51</t>
+          <t>0,34; 0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,36</t>
+          <t>0,19; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,32</t>
+          <t>0,18; 0,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,41</t>
+          <t>0,26; 0,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,45</t>
+          <t>0,33; 0,47</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,4</t>
+          <t>0,11; 0,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,45</t>
+          <t>0,26; 0,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,28</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,26</t>
+          <t>0,19; 0,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,37</t>
+          <t>0,2; 0,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,3</t>
+          <t>0,24; 0,36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,32</t>
+          <t>0,13; 0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,17 +1357,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,16</t>
+          <t>0,03; 0,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,19</t>
+          <t>0,05; 0,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,2</t>
+          <t>0,05; 0,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,19</t>
+          <t>0,09; 0,21</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,81</t>
+          <t>0,7; 0,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 0,93</t>
+          <t>0,81; 0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,91</t>
+          <t>0,78; 0,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,43</t>
+          <t>0,38; 0,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,65</t>
+          <t>0,59; 0,67</t>
         </is>
       </c>
     </row>
